--- a/artfynd/A 56750-2025 artfynd.xlsx
+++ b/artfynd/A 56750-2025 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>130158943</v>
       </c>
       <c r="B4" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56750-2025 artfynd.xlsx
+++ b/artfynd/A 56750-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158958</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130158959</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>130158943</v>
       </c>
       <c r="B4" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>130158955</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130158956</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>130158957</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56750-2025 artfynd.xlsx
+++ b/artfynd/A 56750-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130158959</v>
+        <v>130158958</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499134</v>
+        <v>499104</v>
       </c>
       <c r="R2" t="n">
-        <v>7029264</v>
+        <v>7029303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130158958</v>
+        <v>130158959</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499104</v>
+        <v>499134</v>
       </c>
       <c r="R3" t="n">
-        <v>7029303</v>
+        <v>7029264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -930,7 +930,7 @@
         <v>130158943</v>
       </c>
       <c r="B4" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>130158955</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130158956</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>130158957</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56750-2025 artfynd.xlsx
+++ b/artfynd/A 56750-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130158958</v>
+        <v>130158959</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499104</v>
+        <v>499134</v>
       </c>
       <c r="R2" t="n">
-        <v>7029303</v>
+        <v>7029264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130158959</v>
+        <v>130158958</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499134</v>
+        <v>499104</v>
       </c>
       <c r="R3" t="n">
-        <v>7029264</v>
+        <v>7029303</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -930,7 +930,7 @@
         <v>130158943</v>
       </c>
       <c r="B4" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>130158955</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130158956</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>130158957</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56750-2025 artfynd.xlsx
+++ b/artfynd/A 56750-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130158959</v>
+        <v>130158958</v>
       </c>
       <c r="B2" t="n">
         <v>79209</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499134</v>
+        <v>499104</v>
       </c>
       <c r="R2" t="n">
-        <v>7029264</v>
+        <v>7029303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130158958</v>
+        <v>130158959</v>
       </c>
       <c r="B3" t="n">
         <v>79209</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499104</v>
+        <v>499134</v>
       </c>
       <c r="R3" t="n">
-        <v>7029303</v>
+        <v>7029264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -930,7 +930,7 @@
         <v>130158943</v>
       </c>
       <c r="B4" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56750-2025 artfynd.xlsx
+++ b/artfynd/A 56750-2025 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>130158943</v>
       </c>
       <c r="B4" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56750-2025 artfynd.xlsx
+++ b/artfynd/A 56750-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130158958</v>
+        <v>130158955</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499104</v>
+        <v>499132</v>
       </c>
       <c r="R2" t="n">
-        <v>7029303</v>
+        <v>7029415</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -801,14 +801,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130158959</v>
+        <v>130158956</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499134</v>
+        <v>499084</v>
       </c>
       <c r="R3" t="n">
-        <v>7029264</v>
+        <v>7029411</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -927,38 +927,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130158943</v>
+        <v>130158957</v>
       </c>
       <c r="B4" t="n">
-        <v>97822</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499085</v>
+        <v>499115</v>
       </c>
       <c r="R4" t="n">
-        <v>7029366</v>
+        <v>7029376</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,6 +1016,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1034,14 +1053,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130158955</v>
+        <v>130158958</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1072,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499132</v>
+        <v>499104</v>
       </c>
       <c r="R5" t="n">
-        <v>7029415</v>
+        <v>7029303</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1141,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1160,14 +1179,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130158956</v>
+        <v>130158959</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1198,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499084</v>
+        <v>499134</v>
       </c>
       <c r="R6" t="n">
-        <v>7029411</v>
+        <v>7029264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,37 +1305,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130158957</v>
+        <v>130158943</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1324,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499115</v>
+        <v>499085</v>
       </c>
       <c r="R7" t="n">
-        <v>7029376</v>
+        <v>7029366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,26 +1395,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 56750-2025 artfynd.xlsx
+++ b/artfynd/A 56750-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130158955</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130158956</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130158957</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130158958</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130158959</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1409,8 +1439,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130158943</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>